--- a/data/gravel/Ridley Ignite GTX 2025.xlsx
+++ b/data/gravel/Ridley Ignite GTX 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3A5246-8601-D944-B563-F06C2E849A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54C0128-B902-914A-BADE-4CC4A03BE9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="500" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
   <si>
     <t>brand</t>
   </si>
@@ -299,9 +299,6 @@
     <t>fork</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>internal</t>
   </si>
   <si>
@@ -324,6 +321,15 @@
   </si>
   <si>
     <t>Ignite GTX</t>
+  </si>
+  <si>
+    <t>510 which is length of 100 mm fork</t>
+  </si>
+  <si>
+    <t>no indication if this geometry is for full length 100 m suspension fork or for 510 mm rigid fork</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
@@ -697,7 +703,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -721,7 +727,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -729,7 +735,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -737,7 +746,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>8</v>
@@ -905,7 +914,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -925,7 +934,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -937,7 +946,7 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -957,7 +966,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -977,7 +986,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -985,7 +994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -993,7 +1002,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1001,7 +1010,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -1009,17 +1018,20 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -1042,7 +1054,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -1050,7 +1062,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -1078,7 +1090,7 @@
         <v>58.419999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -1086,7 +1098,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -1107,7 +1119,7 @@
         <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -1122,8 +1134,8 @@
       <c r="A36" t="s">
         <v>87</v>
       </c>
-      <c r="B36" t="s">
-        <v>88</v>
+      <c r="B36" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1170,8 +1182,8 @@
       <c r="A43" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>90</v>
+      <c r="B43" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -1263,7 +1275,7 @@
         <v>71</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1291,7 +1303,7 @@
         <v>76</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1299,7 +1311,7 @@
         <v>77</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1312,7 +1324,7 @@
         <v>79</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -1338,7 +1350,7 @@
         <v>83</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Ridley Ignite GTX 2025.xlsx
+++ b/data/gravel/Ridley Ignite GTX 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54C0128-B902-914A-BADE-4CC4A03BE9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3EC359-3902-CE48-AB14-5A689CB51F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="100">
   <si>
     <t>brand</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>https://images.cyclingfactory.be/transform/eyJidWNrZXQiOiJiY2YtYjJiLWltYWdlcyIsImtleSI6IlNCSUlTWFJJRDI5OF9pbWFnZV84ZGE4ZGMyYTliZWUxNDMxZGNlMjk2ZmU4NTI0MGU4ZmU3NDI2N2QwXzM4NDB4LnBuZyIsImVkaXRzIjp7InJlc2l6ZSI6eyJ3aWR0aCI6MTQwMCwid2l0aG91dEVubGFyZ2VtZW50Ijp0cnVlfSwid2VicCI6eyJxdWFsaXR5Ijo2MH19fQ==</t>
   </si>
 </sst>
 </file>
@@ -730,6 +733,11 @@
         <v>92</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+    </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Ridley Ignite GTX 2025.xlsx
+++ b/data/gravel/Ridley Ignite GTX 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3EC359-3902-CE48-AB14-5A689CB51F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6FCF32-CE40-F44D-9009-788CF53CB3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="102">
   <si>
     <t>brand</t>
   </si>
@@ -308,9 +308,6 @@
     <t>size</t>
   </si>
   <si>
-    <t>euros</t>
-  </si>
-  <si>
     <t>https://www.ridley-bikes.com/en_US/bikes/SBIISXRID298</t>
   </si>
   <si>
@@ -333,6 +330,15 @@
   </si>
   <si>
     <t>https://images.cyclingfactory.be/transform/eyJidWNrZXQiOiJiY2YtYjJiLWltYWdlcyIsImtleSI6IlNCSUlTWFJJRDI5OF9pbWFnZV84ZGE4ZGMyYTliZWUxNDMxZGNlMjk2ZmU4NTI0MGU4ZmU3NDI2N2QwXzM4NDB4LnBuZyIsImVkaXRzIjp7InJlc2l6ZSI6eyJ3aWR0aCI6MTQwMCwid2l0aG91dEVubGFyZ2VtZW50Ijp0cnVlfSwid2VicCI6eyJxdWFsaXR5Ijo2MH19fQ==</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Beringen, Flanders, Belgium</t>
+  </si>
+  <si>
+    <t>EUR</t>
   </si>
 </sst>
 </file>
@@ -687,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -706,7 +712,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -730,12 +736,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -743,10 +749,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1031,7 +1037,7 @@
         <v>39</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -1127,7 +1133,7 @@
         <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -1143,7 +1149,7 @@
         <v>87</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1358,7 +1364,15 @@
         <v>83</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Ridley Ignite GTX 2025.xlsx
+++ b/data/gravel/Ridley Ignite GTX 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6FCF32-CE40-F44D-9009-788CF53CB3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4468B542-C21B-EA44-917E-63F38A7BDDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,24 @@
   </si>
   <si>
     <t>EUR</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -693,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1228,150 +1246,180 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50">
-        <v>27.2</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B56">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>71</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>79</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="1">
-        <v>2499</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>99</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>100</v>
       </c>
     </row>

--- a/data/gravel/Ridley Ignite GTX 2025.xlsx
+++ b/data/gravel/Ridley Ignite GTX 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4468B542-C21B-EA44-917E-63F38A7BDDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C48895D-E667-5D43-9752-2EC323758530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="540" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9720" yWindow="500" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -311,24 +311,12 @@
     <t>https://www.ridley-bikes.com/en_US/bikes/SBIISXRID298</t>
   </si>
   <si>
-    <t>a8:f31</t>
-  </si>
-  <si>
     <t>hardtail</t>
   </si>
   <si>
     <t>Ignite GTX</t>
   </si>
   <si>
-    <t>510 which is length of 100 mm fork</t>
-  </si>
-  <si>
-    <t>no indication if this geometry is for full length 100 m suspension fork or for 510 mm rigid fork</t>
-  </si>
-  <si>
-    <t>suspension</t>
-  </si>
-  <si>
     <t>https://images.cyclingfactory.be/transform/eyJidWNrZXQiOiJiY2YtYjJiLWltYWdlcyIsImtleSI6IlNCSUlTWFJJRDI5OF9pbWFnZV84ZGE4ZGMyYTliZWUxNDMxZGNlMjk2ZmU4NTI0MGU4ZmU3NDI2N2QwXzM4NDB4LnBuZyIsImVkaXRzIjp7InJlc2l6ZSI6eyJ3aWR0aCI6MTQwMCwid2l0aG91dEVubGFyZ2VtZW50Ijp0cnVlfSwid2VicCI6eyJxdWFsaXR5Ijo2MH19fQ==</t>
   </si>
   <si>
@@ -357,13 +345,28 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>rigid</t>
+  </si>
+  <si>
+    <t>a8:f33</t>
+  </si>
+  <si>
+    <t>rigid fork seems to be the default</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -388,6 +391,11 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -409,12 +417,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -711,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -730,7 +739,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -759,7 +768,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -767,10 +776,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -792,6 +798,9 @@
       <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -801,10 +810,10 @@
       <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -946,7 +955,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -966,7 +975,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -978,7 +987,7 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -998,7 +1007,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1018,7 +1027,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1026,364 +1035,411 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22">
+        <f>MEDIAN($G22:$K22)</f>
+        <v>498.16500000000002</v>
+      </c>
+      <c r="D22">
+        <f t="shared" ref="D22:F22" si="0">MEDIAN($G22:$K22)</f>
+        <v>498.16500000000002</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>498.16500000000002</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>498.16500000000002</v>
+      </c>
+      <c r="G22">
+        <v>495.33600000000001</v>
+      </c>
+      <c r="H22">
+        <v>496.745</v>
+      </c>
+      <c r="I22">
+        <v>498.32600000000002</v>
+      </c>
+      <c r="J22">
+        <v>501.08800000000002</v>
+      </c>
+      <c r="K22">
+        <v>498.16500000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23">
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <v>100</v>
+      </c>
+      <c r="E23">
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>36</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>37</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B26" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>38</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B27" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>39</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>41</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B29" t="s">
         <v>41</v>
       </c>
-      <c r="C27">
+      <c r="C29">
         <v>700</v>
       </c>
-      <c r="D27">
+      <c r="D29">
         <v>700</v>
       </c>
-      <c r="E27">
+      <c r="E29">
         <v>700</v>
       </c>
-      <c r="F27">
+      <c r="F29">
         <v>700</v>
       </c>
-      <c r="G27">
+      <c r="G29">
         <v>700</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>42</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>43</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>43</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <f>2.3*25.4</f>
         <v>58.419999999999995</v>
       </c>
-      <c r="D29">
-        <f t="shared" ref="D29:G29" si="0">2.3*25.4</f>
+      <c r="D31">
+        <f t="shared" ref="D31:G31" si="1">2.3*25.4</f>
         <v>58.419999999999995</v>
       </c>
-      <c r="E29">
-        <f t="shared" si="0"/>
+      <c r="E31">
+        <f t="shared" si="1"/>
         <v>58.419999999999995</v>
       </c>
-      <c r="F29">
-        <f t="shared" si="0"/>
+      <c r="F31">
+        <f t="shared" si="1"/>
         <v>58.419999999999995</v>
       </c>
-      <c r="G29">
-        <f t="shared" si="0"/>
+      <c r="G31">
+        <f t="shared" si="1"/>
         <v>58.419999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>44</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>84</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>52</v>
       </c>
-      <c r="B40">
+      <c r="B42">
         <f>2.3*25.4</f>
         <v>58.419999999999995</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42">
-        <v>100</v>
-      </c>
-    </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>55</v>
-      </c>
-      <c r="B43" s="1">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B44">
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>57</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46">
-        <v>148</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47">
-        <v>110</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>58</v>
+      </c>
+      <c r="B48">
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>59</v>
+      </c>
+      <c r="B49">
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56">
-        <v>27.2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>89</v>
@@ -1391,36 +1447,49 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" s="1">
-        <v>2499</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>82</v>
+        <v>80</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2499</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>99</v>
-      </c>
-      <c r="B78" t="s">
-        <v>100</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>95</v>
+      </c>
+      <c r="B80" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Ridley Ignite GTX 2025.xlsx
+++ b/data/gravel/Ridley Ignite GTX 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C48895D-E667-5D43-9752-2EC323758530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F8D326-3EEC-8741-99FB-957B7DAA9E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="500" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3260" yWindow="500" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -1031,9 +1031,6 @@
       <c r="A21" t="s">
         <v>35</v>
       </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1076,16 +1073,16 @@
         <v>105</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
